--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.32314629617537</v>
+        <v>8.177511273128497</v>
       </c>
       <c r="D2" t="n">
-        <v>44.44737571724058</v>
+        <v>7.222698554051595</v>
       </c>
       <c r="E2" t="n">
-        <v>19.704798301471</v>
+        <v>3.202029723989038</v>
       </c>
       <c r="F2" t="n">
-        <v>13.56609994749541</v>
+        <v>2.204491241468005</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.31317752194923</v>
+        <v>12.56339134731675</v>
       </c>
       <c r="D3" t="n">
-        <v>7.593127620522488</v>
+        <v>1.233883238334904</v>
       </c>
       <c r="E3" t="n">
-        <v>19.704798301471</v>
+        <v>3.202029723989038</v>
       </c>
       <c r="F3" t="n">
-        <v>13.56609994749541</v>
+        <v>2.204491241468005</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.98814740652583</v>
+        <v>3.735573953560447</v>
       </c>
       <c r="D4" t="n">
-        <v>21.53215114360954</v>
+        <v>3.49897456083655</v>
       </c>
       <c r="E4" t="n">
-        <v>19.704798301471</v>
+        <v>3.202029723989038</v>
       </c>
       <c r="F4" t="n">
-        <v>13.56609994749541</v>
+        <v>2.204491241468005</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.18612820763653</v>
+        <v>6.205245833740936</v>
       </c>
       <c r="D5" t="n">
-        <v>39.44426001974963</v>
+        <v>6.409692253209315</v>
       </c>
       <c r="E5" t="n">
-        <v>19.704798301471</v>
+        <v>3.202029723989038</v>
       </c>
       <c r="F5" t="n">
-        <v>13.56609994749541</v>
+        <v>2.204491241468005</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.34542210825122</v>
+        <v>5.256131092590824</v>
       </c>
       <c r="D6" t="n">
-        <v>18.4438987687415</v>
+        <v>2.997133549920493</v>
       </c>
       <c r="E6" t="n">
-        <v>19.704798301471</v>
+        <v>3.202029723989038</v>
       </c>
       <c r="F6" t="n">
-        <v>13.56609994749541</v>
+        <v>2.204491241468005</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.597667186327156</v>
+        <v>1.559620917778163</v>
       </c>
       <c r="D7" t="n">
-        <v>9.545053762728367</v>
+        <v>1.55107123644336</v>
       </c>
       <c r="E7" t="n">
-        <v>19.704798301471</v>
+        <v>3.202029723989038</v>
       </c>
       <c r="F7" t="n">
-        <v>13.56609994749541</v>
+        <v>2.204491241468005</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.55214049201726</v>
+        <v>2.364722829952804</v>
       </c>
       <c r="D8" t="n">
-        <v>10.74816844862417</v>
+        <v>1.746577372901428</v>
       </c>
       <c r="E8" t="n">
-        <v>19.704798301471</v>
+        <v>3.202029723989038</v>
       </c>
       <c r="F8" t="n">
-        <v>13.56609994749541</v>
+        <v>2.204491241468005</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.67539808438917</v>
+        <v>3.847252188713239</v>
       </c>
       <c r="D9" t="n">
-        <v>18.91004610116854</v>
+        <v>3.072882491439887</v>
       </c>
       <c r="E9" t="n">
-        <v>19.704798301471</v>
+        <v>3.202029723989038</v>
       </c>
       <c r="F9" t="n">
-        <v>13.56609994749541</v>
+        <v>2.204491241468005</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.77921046841143</v>
+        <v>7.439121701116857</v>
       </c>
       <c r="D10" t="n">
-        <v>40.89130205005003</v>
+        <v>6.64483658313313</v>
       </c>
       <c r="E10" t="n">
-        <v>19.704798301471</v>
+        <v>3.202029723989038</v>
       </c>
       <c r="F10" t="n">
-        <v>13.56609994749541</v>
+        <v>2.204491241468005</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
